--- a/logs/Log_Erro.xlsx
+++ b/logs/Log_Erro.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\03-Relatorios\Projecoes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\01-Usuario\Daniel\Modelo Vendas Diário\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD2C535-F9E0-4D9D-A2E6-4077557ABC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06277633-5A31-4B19-8492-6A4971F1FDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22F64FCD-74D6-427D-A4A9-E7BB04287290}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{22F64FCD-74D6-427D-A4A9-E7BB04287290}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Data</t>
   </si>
@@ -144,8 +145,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{55ED3444-8803-4BED-8647-C44CB71DF079}" name="Tabela1" displayName="Tabela1" ref="A1:C18" totalsRowShown="0">
-  <autoFilter ref="A1:C18" xr:uid="{55ED3444-8803-4BED-8647-C44CB71DF079}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{55ED3444-8803-4BED-8647-C44CB71DF079}" name="Tabela1" displayName="Tabela1" ref="A1:C19" totalsRowShown="0">
+  <autoFilter ref="A1:C19" xr:uid="{55ED3444-8803-4BED-8647-C44CB71DF079}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{77AB6C24-4337-4DFF-8580-700FDB224A55}" name="Data" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{701D7B81-C828-48EE-B13D-F1DB999A4884}" name="Sistema Erro"/>
@@ -472,15 +473,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567E8EE9-5E50-4490-AB9C-0132C0A6F615}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,7 +492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>45694</v>
       </c>
@@ -502,7 +503,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>45714</v>
       </c>
@@ -513,7 +514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>45721</v>
       </c>
@@ -524,7 +525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>45723</v>
       </c>
@@ -535,7 +536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>45740</v>
       </c>
@@ -546,7 +547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45769</v>
       </c>
@@ -557,7 +558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>45799</v>
       </c>
@@ -568,7 +569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45820</v>
       </c>
@@ -579,7 +580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>45831</v>
       </c>
@@ -590,7 +591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45835</v>
       </c>
@@ -601,7 +602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45841</v>
       </c>
@@ -612,7 +613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>45943</v>
       </c>
@@ -623,7 +624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>45954</v>
       </c>
@@ -634,7 +635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>45959</v>
       </c>
@@ -645,7 +646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>45995</v>
       </c>
@@ -656,7 +657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46058</v>
       </c>
@@ -667,7 +668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46114</v>
       </c>
@@ -675,6 +676,17 @@
         <v>15</v>
       </c>
       <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19">
         <v>2</v>
       </c>
     </row>
